--- a/pacjenci/JOANNA KLĘP.xlsx
+++ b/pacjenci/JOANNA KLĘP.xlsx
@@ -483,7 +483,11 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -523,7 +527,11 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -563,7 +571,11 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Do oceny</t>

--- a/pacjenci/JOANNA KLĘP.xlsx
+++ b/pacjenci/JOANNA KLĘP.xlsx
@@ -413,191 +413,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>19.04.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak śródpiersia z obwodowych lifmocytów B. Ocena stopnia zaawansowania.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 90mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Asymetria pobudzenia metabolicznego w prawym fałdzie nalewkowo-nagłośniowym SUV max 2,7.   Klatka piersiowa i śródpiersie: Aktywny metabolicznie obszar w śródpiersiu po stronie prawej wielkości wg PET 11x17x20mm, SUV max 4,6 w obrębie masy położonej zamostkowo w śródpiersiu przednim o orientacyjnym wymiarze wg TK 46x46x43mm [lm TK 103] - dokładana ocena możliwa w badaniu z kontrastem i.v. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym. Drobne zwapnienie w segm. 2 płuca prawego. Obniżenie cieniowania wątroby do 37 HU.  Brzuch i miednica: Pobudzenie metaboliczne w endometrium SUV max 2,6 - czynnościowe ? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatia L5/S1.  Wartości referencyjne: MBPS SUVmax 1,6, Prawy płat wątroby SUVmax do 2,3.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie naciek chłoniakowy w obrębie masy miękkotkankowej w śródpiersiu.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>4.6</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>21.06.2021</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak śródpiersia z obwodowych limfocytów B. Ocena odpowiedzi na zastosowane leczenia po 4 cyklach chemioterapii R-CHOP-14+metotreksat ith.  OPIS: Ibraheem Al Maraih</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 63 min od podania 18F-FDG. Glikemia: 86mg%</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Asymetryczne pobudzenie metabolicznie w topografii prawym fałdzie nalewkowo-nagłośniowym, SUV max 4,1- do ew. kontroli laryngologicznej.   Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zwapnienie w segm. 2 płuca prawego. W śródpiersiu po stronie prawej widoczne zagęszczenie miękkotkankowe o wym. ok. 33x17 mm [Im TK 300] - w pierwszej kolejności przerośnieta grasica.  NIeznacznie zwiększona ilość płynu w worku osierdziowym.   Brzuch i miednica: Pobudzenie metaboliczne w endometrium SUV max 3,7 - czynnościowe ? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Obniżenie cieniowania wątroby do 37 HU. Pęcherzyk - czynnościowy ? 20mm w przydatkach lewych.  Inne: Śladowe gromadzenie FDG w topografii drobnego obszaru w tkance podskórnej prawego ramienia - do ew. kontroli w USG.   Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatia L5/S1.  Wartości referencyjne: MBPS SUVmax 1,8, Prawy płat wątroby SUVmax do 2,2.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>4.1</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>26.08.2021</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak śródpiersia z obwodowych limfocytów B. Ocena remisji choroby po zakończeniu chemioterapii przed ew. kwalifikacją do IFRT.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 73mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. W zachyłku zębodołowym prawej zatoki szczękowej widoczne są korzenie zębów trzonowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim, pośrodkowo i prawobocznie od linii pośrodkowej widoczna jest miękkotkankowa struktura o nieco nieostrych obrysach i wymiarach ok. 17x14mm [Im TK 280] - w pierwszej kolejności masa resztkowa.  Zwiększona ilość płynu w worku osierdziowym, o szerokości płaszcza do 7mm w okolicy koniuszkowej PK oraz do 12mm przy podstawie PK serca - do oceny w Echokardiografii. Drobne zwapnienie w segm. 2 płuca prawego. Niewielkie zmiany włókniste w segm. 5 płuca prawego oraz naprzeponowo po stronie lewej.  Brzuch i miednica: Pobudzenie metaboliczne w jamie macicy i w topografii endometrium  - czynnościowe? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Dyskopatia na poziomie L5/S1. Ubytek osteolityczny o śr. 4,4mm w wyrostku stawowym prawego małego stawu miedzykręgowego na poziomie L3/L4, z ubytkiem warstwy korowej. Drobne wyspy kostne w głowie prawej kości ramiennej i prawej kości udowej.  Inne: Pobudzenie metaboliczne w tkance bruntanej szyi i KLP.    Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 2,7.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech obecności aktywnej metabolicznie choroby chłoniakowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>2.7</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/JOANNA KLĘP.xlsx
+++ b/pacjenci/JOANNA KLĘP.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 90mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Asymetria pobudzenia metabolicznego w prawym fałdzie nalewkowo-nagłośniowym SUV max 2,7.   Klatka piersiowa i śródpiersie: Aktywny metabolicznie obszar w śródpiersiu po stronie prawej wielkości wg PET 11x17x20mm, SUV max 4,6 w obrębie masy położonej zamostkowo w śródpiersiu przednim o orientacyjnym wymiarze wg TK 46x46x43mm [lm TK 103] - dokładana ocena możliwa w badaniu z kontrastem i.v. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym. Drobne zwapnienie w segm. 2 płuca prawego. Obniżenie cieniowania wątroby do 37 HU.  Brzuch i miednica: Pobudzenie metaboliczne w endometrium SUV max 2,6 - czynnościowe ? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatia L5/S1.  Wartości referencyjne: MBPS SUVmax 1,6, Prawy płat wątroby SUVmax do 2,3.</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Asymetria pobudzenia metabolicznego w prawym fałdzie nalewkowo-nagłośniowym SUV max 2,7.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w śródpiersiu po stronie prawej wielkości wg PET 11x17x20mm, SUV max 4,6 w obrębie masy położonej zamostkowo w śródpiersiu przednim o orientacyjnym wymiarze wg TK 46x46x43mm [lm TK 103] - dokładana ocena możliwa w badaniu z kontrastem i.v. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym. Drobne zwapnienie w segm. 2 płuca prawego. Obniżenie cieniowania wątroby do 37 HU.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w endometrium SUV max 2,6 - czynnościowe ? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatia L5/S1.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie naciek chłoniakowy w obrębie masy miękkotkankowej w śródpiersiu.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>4.6</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 63 min od podania 18F-FDG. Glikemia: 86mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Asymetryczne pobudzenie metabolicznie w topografii prawym fałdzie nalewkowo-nagłośniowym, SUV max 4,1- do ew. kontroli laryngologicznej.   Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zwapnienie w segm. 2 płuca prawego. W śródpiersiu po stronie prawej widoczne zagęszczenie miękkotkankowe o wym. ok. 33x17 mm [Im TK 300] - w pierwszej kolejności przerośnieta grasica.  NIeznacznie zwiększona ilość płynu w worku osierdziowym.   Brzuch i miednica: Pobudzenie metaboliczne w endometrium SUV max 3,7 - czynnościowe ? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Obniżenie cieniowania wątroby do 37 HU. Pęcherzyk - czynnościowy ? 20mm w przydatkach lewych.  Inne: Śladowe gromadzenie FDG w topografii drobnego obszaru w tkance podskórnej prawego ramienia - do ew. kontroli w USG.   Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatia L5/S1.  Wartości referencyjne: MBPS SUVmax 1,8, Prawy płat wątroby SUVmax do 2,2.</t>
+          <t>86</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Asymetryczne pobudzenie metabolicznie w topografii prawym fałdzie nalewkowo-nagłośniowym, SUV max 4,1- do ew. kontroli laryngologicznej.   Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zwapnienie w segm. 2 płuca prawego. W śródpiersiu po stronie prawej widoczne zagęszczenie miękkotkankowe o wym. ok. 33x17 mm [Im TK 300] - w pierwszej kolejności przerośnieta grasica.  NIeznacznie zwiększona ilość płynu w worku osierdziowym.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w endometrium SUV max 3,7 - czynnościowe ? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Obniżenie cieniowania wątroby do 37 HU. Pęcherzyk - czynnościowy ? 20mm w przydatkach lewych.  Inne: Śladowe gromadzenie FDG w topografii drobnego obszaru w tkance podskórnej prawego ramienia - do ew. kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Dyskopatia L5/S1.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>4.1</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 73mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. W zachyłku zębodołowym prawej zatoki szczękowej widoczne są korzenie zębów trzonowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim, pośrodkowo i prawobocznie od linii pośrodkowej widoczna jest miękkotkankowa struktura o nieco nieostrych obrysach i wymiarach ok. 17x14mm [Im TK 280] - w pierwszej kolejności masa resztkowa.  Zwiększona ilość płynu w worku osierdziowym, o szerokości płaszcza do 7mm w okolicy koniuszkowej PK oraz do 12mm przy podstawie PK serca - do oceny w Echokardiografii. Drobne zwapnienie w segm. 2 płuca prawego. Niewielkie zmiany włókniste w segm. 5 płuca prawego oraz naprzeponowo po stronie lewej.  Brzuch i miednica: Pobudzenie metaboliczne w jamie macicy i w topografii endometrium  - czynnościowe? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Dyskopatia na poziomie L5/S1. Ubytek osteolityczny o śr. 4,4mm w wyrostku stawowym prawego małego stawu miedzykręgowego na poziomie L3/L4, z ubytkiem warstwy korowej. Drobne wyspy kostne w głowie prawej kości ramiennej i prawej kości udowej.  Inne: Pobudzenie metaboliczne w tkance bruntanej szyi i KLP.    Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 2,7.</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. W zachyłku zębodołowym prawej zatoki szczękowej widoczne są korzenie zębów trzonowych.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W śródpiersiu przednim, pośrodkowo i prawobocznie od linii pośrodkowej widoczna jest miękkotkankowa struktura o nieco nieostrych obrysach i wymiarach ok. 17x14mm [Im TK 280] - w pierwszej kolejności masa resztkowa.  Zwiększona ilość płynu w worku osierdziowym, o szerokości płaszcza do 7mm w okolicy koniuszkowej PK oraz do 12mm przy podstawie PK serca - do oceny w Echokardiografii. Drobne zwapnienie w segm. 2 płuca prawego. Niewielkie zmiany włókniste w segm. 5 płuca prawego oraz naprzeponowo po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w jamie macicy i w topografii endometrium  - czynnościowe? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Dyskopatia na poziomie L5/S1. Ubytek osteolityczny o śr. 4,4mm w wyrostku stawowym prawego małego stawu miedzykręgowego na poziomie L3/L4, z ubytkiem warstwy korowej. Drobne wyspy kostne w głowie prawej kości ramiennej i prawej kości udowej.  Inne: Pobudzenie metaboliczne w tkance bruntanej szyi i KLP.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech obecności aktywnej metabolicznie choroby chłoniakowej. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>2.7</v>
       </c>
     </row>
